--- a/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A05_A06_세부요청표_20261028_담당자반영.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A05_A06_세부요청표_20261028_담당자반영.xlsx
@@ -555,7 +555,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 권고일 2026-11-02</t>
+          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-02</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: 박철호 부장 · 권고일 2026-11-04</t>
+          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-04</t>
         </is>
       </c>
     </row>
